--- a/data/wines.xlsx
+++ b/data/wines.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X131"/>
+  <dimension ref="A1:Z131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -564,6 +564,16 @@
           <t>Vivino URL (비우면 자동 검색링크)</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>프로필 상태 (estimated=추정 / verified=시음 검수)</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>품종 태그 (쉼표 구분, 비우면 품종 컬럼에서 자동 생성)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -662,6 +672,16 @@
         <v>4</v>
       </c>
       <c r="X2" s="2" t="inlineStr"/>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>카베르네 소비뇽, 메를로</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -760,6 +780,16 @@
         <v>3</v>
       </c>
       <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t>메를로</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -855,6 +885,16 @@
         <v>1</v>
       </c>
       <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t>샤도네이, 피노 누아, 피노 뫼니에</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -955,6 +995,16 @@
         <v>1</v>
       </c>
       <c r="X5" s="2" t="inlineStr"/>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>샤도네이</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1045,6 +1095,16 @@
         <v>1</v>
       </c>
       <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>샤도네이, 피노 누아, 피노 뫼니에</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1147,6 +1207,16 @@
         <v>1</v>
       </c>
       <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>샤도네이</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1237,6 +1307,16 @@
         <v>1</v>
       </c>
       <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>샤도네이, 피노 뫼니에</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1331,6 +1411,16 @@
         <v>1</v>
       </c>
       <c r="X9" s="2" t="inlineStr"/>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>피노 누아, 샤도네이, 피노 뫼니에</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1426,6 +1516,16 @@
         <v>1</v>
       </c>
       <c r="X10" s="2" t="inlineStr"/>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>소비뇽 블랑, 세미용</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1520,6 +1620,16 @@
         <v>4</v>
       </c>
       <c r="X11" s="2" t="inlineStr"/>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>카베르네 소비뇽, 메를로, 카베르네 프랑</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1614,6 +1724,16 @@
         <v>1</v>
       </c>
       <c r="X12" s="2" t="inlineStr"/>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>소비뇽 블랑, 세미용, 슈냉 블랑</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1706,6 +1826,16 @@
         <v>1</v>
       </c>
       <c r="X13" s="2" t="inlineStr"/>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>세미용, 소비뇽 블랑, 뮈스카델</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1796,6 +1926,16 @@
         <v>1</v>
       </c>
       <c r="X14" s="2" t="inlineStr"/>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>소비뇽 블랑, 세미용</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1886,6 +2026,16 @@
         <v>4</v>
       </c>
       <c r="X15" s="2" t="inlineStr"/>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>메를로, 말벡</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1974,6 +2124,16 @@
         <v>1</v>
       </c>
       <c r="X16" s="2" t="inlineStr"/>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>소비뇽 그리, 뮈스카델</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2069,6 +2229,16 @@
         <v>4</v>
       </c>
       <c r="X17" s="2" t="inlineStr"/>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>메를로, 카베르네 소비뇽, 카베르네 프랑</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2164,6 +2334,16 @@
         <v>4</v>
       </c>
       <c r="X18" s="2" t="inlineStr"/>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>말벡, 메를로, 타나</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2263,6 +2443,16 @@
         <v>3</v>
       </c>
       <c r="X19" s="2" t="inlineStr"/>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>가르나차, 시라, 까리냥</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2358,6 +2548,16 @@
         <v>3</v>
       </c>
       <c r="X20" s="2" t="inlineStr"/>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>가르나차, 무르베드르, 시라</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2442,6 +2642,16 @@
         <v>1</v>
       </c>
       <c r="X21" s="2" t="inlineStr"/>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>콜롬바드, 소비뇽 블랑</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2533,6 +2743,16 @@
         <v>3</v>
       </c>
       <c r="X22" s="2" t="inlineStr"/>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>까리냥</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2623,6 +2843,16 @@
         <v>3</v>
       </c>
       <c r="X23" s="2" t="inlineStr"/>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>메를로</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2724,6 +2954,16 @@
         <v>1</v>
       </c>
       <c r="X24" s="2" t="inlineStr"/>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>샤도네이, 피노 누아</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2825,6 +3065,16 @@
         <v>1</v>
       </c>
       <c r="X25" s="2" t="inlineStr"/>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>샤도네이, 피노 누아</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2924,6 +3174,16 @@
         <v>1</v>
       </c>
       <c r="X26" s="2" t="inlineStr"/>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>샤도네이</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -3019,6 +3279,16 @@
         <v>1</v>
       </c>
       <c r="X27" s="2" t="inlineStr"/>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>샤도네이, 피노 누아</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -3115,6 +3385,16 @@
         <v>1</v>
       </c>
       <c r="X28" s="2" t="inlineStr"/>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>피노 누아, 샤도네이</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -3212,6 +3492,16 @@
         <v>1</v>
       </c>
       <c r="X29" s="2" t="inlineStr"/>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>샤도네이</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -3308,6 +3598,16 @@
         <v>1</v>
       </c>
       <c r="X30" s="2" t="inlineStr"/>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>피노 누아</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -3402,6 +3702,16 @@
         <v>1</v>
       </c>
       <c r="X31" s="2" t="inlineStr"/>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>피노 누아</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -3488,6 +3798,16 @@
         <v>1</v>
       </c>
       <c r="X32" s="2" t="inlineStr"/>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>샤도네이</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -3572,6 +3892,16 @@
         <v>1</v>
       </c>
       <c r="X33" s="2" t="inlineStr"/>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>샤도네이, 피노 누아</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3656,6 +3986,16 @@
         <v>1</v>
       </c>
       <c r="X34" s="2" t="inlineStr"/>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>샤도네이, 피노 누아</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -3750,6 +4090,16 @@
         <v>1</v>
       </c>
       <c r="X35" s="2" t="inlineStr"/>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>베르멘티노</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3845,6 +4195,16 @@
         <v>1</v>
       </c>
       <c r="X36" s="2" t="inlineStr"/>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>오르피키오</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3939,6 +4299,16 @@
         <v>3</v>
       </c>
       <c r="X37" s="2" t="inlineStr"/>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>산지오베제, 콜로리노</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -4033,6 +4403,16 @@
         <v>4</v>
       </c>
       <c r="X38" s="2" t="inlineStr"/>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>산지오베제, 카베르네 소비뇽</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -4132,6 +4512,16 @@
         <v>3</v>
       </c>
       <c r="X39" s="2" t="inlineStr"/>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>산지오베제, 콜로리노</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -4226,6 +4616,16 @@
         <v>3</v>
       </c>
       <c r="X40" s="2" t="inlineStr"/>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>산지오베제</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -4325,6 +4725,16 @@
         <v>1</v>
       </c>
       <c r="X41" s="2" t="inlineStr"/>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>베르멘티노, 트레비아노, 말바시아, 소비뇽 블랑</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -4424,6 +4834,16 @@
         <v>4</v>
       </c>
       <c r="X42" s="2" t="inlineStr"/>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>메를로, 시라, 쁘띠 베르도, 산지오베제</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -4523,6 +4943,16 @@
         <v>4</v>
       </c>
       <c r="X43" s="2" t="inlineStr"/>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>카베르네 소비뇽, 메를로, 산지오베제</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -4619,6 +5049,16 @@
         <v>1</v>
       </c>
       <c r="X44" s="2" t="inlineStr"/>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>트레비아노</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -4717,6 +5157,16 @@
         <v>3</v>
       </c>
       <c r="X45" s="2" t="inlineStr"/>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>산지오베제</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -4816,6 +5266,16 @@
         <v>4</v>
       </c>
       <c r="X46" s="2" t="inlineStr"/>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>시라, 메를로, 카베르네 소비뇽</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -4911,6 +5371,16 @@
         <v>3</v>
       </c>
       <c r="X47" s="2" t="inlineStr"/>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>프리미티보, 네그로아마로</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -5005,6 +5475,16 @@
         <v>3</v>
       </c>
       <c r="X48" s="2" t="inlineStr"/>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>프리미티보, 네그로아마로</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -5093,6 +5573,16 @@
         <v>1</v>
       </c>
       <c r="X49" s="2" t="inlineStr"/>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>베르디키오</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -5192,6 +5682,16 @@
         <v>3</v>
       </c>
       <c r="X50" s="2" t="inlineStr"/>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>베르나차 네라</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -5284,6 +5784,16 @@
         <v>4</v>
       </c>
       <c r="X51" s="2" t="inlineStr"/>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>카베르네 소비뇽, 산지오베제, 메를로</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -5378,6 +5888,16 @@
         <v>1</v>
       </c>
       <c r="X52" s="2" t="inlineStr"/>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>트레비아노</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -5472,6 +5992,16 @@
         <v>4</v>
       </c>
       <c r="X53" s="2" t="inlineStr"/>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>몬테풀치아노</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -5569,6 +6099,16 @@
         <v>4</v>
       </c>
       <c r="X54" s="2" t="inlineStr"/>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>몬테풀치아노</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -5668,6 +6208,16 @@
         <v>3</v>
       </c>
       <c r="X55" s="2" t="inlineStr"/>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>프리미티보</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -5769,6 +6319,16 @@
         <v>3</v>
       </c>
       <c r="X56" s="2" t="inlineStr"/>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>프리미티보, 네그로아마로</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -5862,6 +6422,16 @@
         <v>1</v>
       </c>
       <c r="X57" s="2" t="inlineStr"/>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>모스카토</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -5955,6 +6525,16 @@
         <v>1</v>
       </c>
       <c r="X58" s="2" t="inlineStr"/>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>피노 그리지오</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -6050,6 +6630,16 @@
         <v>1</v>
       </c>
       <c r="X59" s="2" t="inlineStr"/>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>루레이로, 아린토, 트라자두라, 페르낭 피레스</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -6145,6 +6735,16 @@
         <v>2</v>
       </c>
       <c r="X60" s="2" t="inlineStr"/>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>아잘, 토우리가 나시오날, 에스파데이로</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -6245,6 +6845,16 @@
         <v>1</v>
       </c>
       <c r="X61" s="2" t="inlineStr"/>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>루레이로, 알바리뇨</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -6341,6 +6951,16 @@
         <v>1</v>
       </c>
       <c r="X62" s="2" t="inlineStr"/>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>루레이로</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -6441,6 +7061,16 @@
         <v>1</v>
       </c>
       <c r="X63" s="2" t="inlineStr"/>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>알바리뇨</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -6525,6 +7155,16 @@
         <v>1</v>
       </c>
       <c r="X64" s="2" t="inlineStr"/>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>아린토, 루레이로</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -6624,6 +7264,16 @@
         <v>1</v>
       </c>
       <c r="X65" s="2" t="inlineStr"/>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>알바리뇨</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -6714,6 +7364,16 @@
         <v>1</v>
       </c>
       <c r="X66" s="2" t="inlineStr"/>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>알바리뇨</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -6812,6 +7472,16 @@
         <v>1</v>
       </c>
       <c r="X67" s="2" t="inlineStr"/>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>알바리뇨</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -6906,6 +7576,16 @@
         <v>1</v>
       </c>
       <c r="X68" s="2" t="inlineStr"/>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>루레이로</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -6998,6 +7678,16 @@
         <v>1</v>
       </c>
       <c r="X69" s="2" t="inlineStr"/>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>루레이로</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -7092,6 +7782,16 @@
         <v>1</v>
       </c>
       <c r="X70" s="2" t="inlineStr"/>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>페르낭 피레스, 모스카텔</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -7192,6 +7892,16 @@
         <v>4</v>
       </c>
       <c r="X71" s="2" t="inlineStr"/>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>시라, 알리칸테 부셰, 토우리가 나시오날</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -7276,6 +7986,16 @@
         <v>1</v>
       </c>
       <c r="X72" s="2" t="inlineStr"/>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>소비뇽 블랑, 비오시뉴, 베르데호, 비오니에</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -7372,6 +8092,16 @@
         <v>3</v>
       </c>
       <c r="X73" s="2" t="inlineStr"/>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>카스텔라오, 트린카데이라, 템프라니요</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -7466,6 +8196,16 @@
         <v>1</v>
       </c>
       <c r="X74" s="2" t="inlineStr"/>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>비오니에, 아린토</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -7565,6 +8305,16 @@
         <v>4</v>
       </c>
       <c r="X75" s="2" t="inlineStr"/>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>카스텔라오, 토우리가 나시오날, 토우리가 프랑카</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -7655,6 +8405,16 @@
         <v>3</v>
       </c>
       <c r="X76" s="2" t="inlineStr"/>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>카스텔라오</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -7745,6 +8505,16 @@
         <v>4</v>
       </c>
       <c r="X77" s="2" t="inlineStr"/>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>카스텔라오, 카베르네 소비뇽, 틴타 프란시스카</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -7844,6 +8614,16 @@
         <v>1</v>
       </c>
       <c r="X78" s="2" t="inlineStr"/>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>모스카텔</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -7938,6 +8718,16 @@
         <v>1</v>
       </c>
       <c r="X79" s="2" t="inlineStr"/>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>모스카텔</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -8032,6 +8822,16 @@
         <v>1</v>
       </c>
       <c r="X80" s="2" t="inlineStr"/>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>모스카텔</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -8125,6 +8925,12 @@
         <v>1</v>
       </c>
       <c r="X81" s="2" t="inlineStr"/>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -8215,6 +9021,16 @@
         <v>2</v>
       </c>
       <c r="X82" s="2" t="inlineStr"/>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>템프라니요, 시라, 토우리가 나시오날, 카스텔라오</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -8316,6 +9132,16 @@
         <v>1</v>
       </c>
       <c r="X83" s="2" t="inlineStr"/>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>모스카텔</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -8411,6 +9237,16 @@
         <v>1</v>
       </c>
       <c r="X84" s="2" t="inlineStr"/>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>모스카텔</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -8508,6 +9344,16 @@
         <v>1</v>
       </c>
       <c r="X85" s="2" t="inlineStr"/>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>모스카텔</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -8605,6 +9451,16 @@
         <v>1</v>
       </c>
       <c r="X86" s="2" t="inlineStr"/>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>모스카텔</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -8708,6 +9564,16 @@
         <v>1</v>
       </c>
       <c r="X87" s="2" t="inlineStr"/>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>모스카텔</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -8806,6 +9672,16 @@
         <v>1</v>
       </c>
       <c r="X88" s="2" t="inlineStr"/>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>모스카텔</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -8896,6 +9772,16 @@
         <v>1</v>
       </c>
       <c r="X89" s="2" t="inlineStr"/>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>모스카텔</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -8992,6 +9878,16 @@
         <v>1</v>
       </c>
       <c r="X90" s="2" t="inlineStr"/>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>모스카텔</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -9084,6 +9980,16 @@
         <v>2</v>
       </c>
       <c r="X91" s="2" t="inlineStr"/>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>시라</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -9178,6 +10084,16 @@
         <v>3</v>
       </c>
       <c r="X92" s="2" t="inlineStr"/>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>템프라니요, 트린카데이라, 시라, 알리칸테 부셰</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -9276,6 +10192,16 @@
         <v>3</v>
       </c>
       <c r="X93" s="2" t="inlineStr"/>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>그랑 누아, 트린카데이라, 템프라니요</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -9370,6 +10296,16 @@
         <v>3</v>
       </c>
       <c r="X94" s="2" t="inlineStr"/>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>그랑 누아, 트린카데이라, 템프라니요</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -9462,6 +10398,16 @@
         <v>1</v>
       </c>
       <c r="X95" s="2" t="inlineStr"/>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>아린토, 비칼, 마리아 고메스, 세르시알</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -9552,6 +10498,16 @@
         <v>2</v>
       </c>
       <c r="X96" s="2" t="inlineStr"/>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>바가</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -9645,6 +10601,16 @@
         <v>1</v>
       </c>
       <c r="X97" s="2" t="inlineStr"/>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>아린토</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -9737,6 +10703,16 @@
         <v>4</v>
       </c>
       <c r="X98" s="2" t="inlineStr"/>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>바가</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -9827,6 +10803,16 @@
         <v>1</v>
       </c>
       <c r="X99" s="2" t="inlineStr"/>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>아잘, 트라자두라, 루레이로, 아린토</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -9917,6 +10903,16 @@
         <v>1</v>
       </c>
       <c r="X100" s="2" t="inlineStr"/>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>알바리뇨</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -10007,6 +11003,16 @@
         <v>1</v>
       </c>
       <c r="X101" s="2" t="inlineStr"/>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>엔크루자도</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -10097,6 +11103,16 @@
         <v>4</v>
       </c>
       <c r="X102" s="2" t="inlineStr"/>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>토우리가 나시오날</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -10185,6 +11201,16 @@
         <v>1</v>
       </c>
       <c r="X103" s="2" t="inlineStr"/>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>시리아, 폰테칼</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -10273,6 +11299,16 @@
         <v>1</v>
       </c>
       <c r="X104" s="2" t="inlineStr"/>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>시리아, 폰테칼</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -10361,6 +11397,16 @@
         <v>3</v>
       </c>
       <c r="X105" s="2" t="inlineStr"/>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>템프라니요, 루페테</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -10450,6 +11496,16 @@
         <v>1</v>
       </c>
       <c r="X106" s="2" t="inlineStr"/>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>아린토, 비칼, 샤도네이</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -10539,6 +11595,16 @@
         <v>4</v>
       </c>
       <c r="X107" s="2" t="inlineStr"/>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>시라, 바가, 토우리가 나시오날, 카베르네 소비뇽</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -10630,6 +11696,16 @@
         <v>1</v>
       </c>
       <c r="X108" s="2" t="inlineStr"/>
+      <c r="Y108" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z108" s="2" t="inlineStr">
+        <is>
+          <t>샤도네이, 아린토</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -10721,6 +11797,16 @@
         <v>4</v>
       </c>
       <c r="X109" s="2" t="inlineStr"/>
+      <c r="Y109" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z109" s="2" t="inlineStr">
+        <is>
+          <t>토우리가 나시오날, 토우리가 프랑카, 템프라니요, 카스텔라오, 알리칸테 부셰</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -10811,6 +11897,12 @@
         <v>1</v>
       </c>
       <c r="X110" s="2" t="inlineStr"/>
+      <c r="Y110" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -10899,6 +11991,16 @@
         <v>4</v>
       </c>
       <c r="X111" s="2" t="inlineStr"/>
+      <c r="Y111" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z111" s="2" t="inlineStr">
+        <is>
+          <t>토우리가 나시오날, 템프라니요</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -10987,6 +12089,16 @@
         <v>2</v>
       </c>
       <c r="X112" s="2" t="inlineStr"/>
+      <c r="Y112" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z112" s="2" t="inlineStr">
+        <is>
+          <t>가르나차, 시라, 피노 누아</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -11075,6 +12187,16 @@
         <v>2</v>
       </c>
       <c r="X113" s="2" t="inlineStr"/>
+      <c r="Y113" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z113" s="2" t="inlineStr">
+        <is>
+          <t>피노 누아, 시라</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -11167,6 +12289,16 @@
         <v>4</v>
       </c>
       <c r="X114" s="2" t="inlineStr"/>
+      <c r="Y114" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z114" s="2" t="inlineStr">
+        <is>
+          <t>템프라니요</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -11257,6 +12389,16 @@
         <v>4</v>
       </c>
       <c r="X115" s="2" t="inlineStr"/>
+      <c r="Y115" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z115" s="2" t="inlineStr">
+        <is>
+          <t>템프라니요, 카베르네 소비뇽</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -11341,6 +12483,16 @@
         <v>4</v>
       </c>
       <c r="X116" s="2" t="inlineStr"/>
+      <c r="Y116" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z116" s="2" t="inlineStr">
+        <is>
+          <t>템프라니요</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -11432,6 +12584,16 @@
         <v>1</v>
       </c>
       <c r="X117" s="2" t="inlineStr"/>
+      <c r="Y117" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z117" s="2" t="inlineStr">
+        <is>
+          <t>리슬링</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -11518,6 +12680,16 @@
         <v>1</v>
       </c>
       <c r="X118" s="2" t="inlineStr"/>
+      <c r="Y118" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z118" s="2" t="inlineStr">
+        <is>
+          <t>리슬링</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -11608,6 +12780,16 @@
         <v>1</v>
       </c>
       <c r="X119" s="2" t="inlineStr"/>
+      <c r="Y119" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z119" s="2" t="inlineStr">
+        <is>
+          <t>리슬링</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -11698,6 +12880,16 @@
         <v>1</v>
       </c>
       <c r="X120" s="2" t="inlineStr"/>
+      <c r="Y120" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z120" s="2" t="inlineStr">
+        <is>
+          <t>오르테가, 옵티마</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -11782,6 +12974,16 @@
         <v>2</v>
       </c>
       <c r="X121" s="2" t="inlineStr"/>
+      <c r="Y121" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z121" s="2" t="inlineStr">
+        <is>
+          <t>피노 누아</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -11866,6 +13068,16 @@
         <v>2</v>
       </c>
       <c r="X122" s="2" t="inlineStr"/>
+      <c r="Y122" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z122" s="2" t="inlineStr">
+        <is>
+          <t>피노 누아</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -11952,6 +13164,16 @@
         <v>1</v>
       </c>
       <c r="X123" s="2" t="inlineStr"/>
+      <c r="Y123" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z123" s="2" t="inlineStr">
+        <is>
+          <t>샤도네이, 비오니에</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -12048,6 +13270,16 @@
         <v>4</v>
       </c>
       <c r="X124" s="2" t="inlineStr"/>
+      <c r="Y124" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z124" s="2" t="inlineStr">
+        <is>
+          <t>타나</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -12138,6 +13370,16 @@
         <v>4</v>
       </c>
       <c r="X125" s="2" t="inlineStr"/>
+      <c r="Y125" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z125" s="2" t="inlineStr">
+        <is>
+          <t>카베르네 소비뇽</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -12228,6 +13470,16 @@
         <v>4</v>
       </c>
       <c r="X126" s="2" t="inlineStr"/>
+      <c r="Y126" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z126" s="2" t="inlineStr">
+        <is>
+          <t>쁘띠 베르도</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -12322,6 +13574,16 @@
         <v>1</v>
       </c>
       <c r="X127" s="2" t="inlineStr"/>
+      <c r="Y127" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z127" s="2" t="inlineStr">
+        <is>
+          <t>샤도네이, 비오니에</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -12418,6 +13680,16 @@
         <v>4</v>
       </c>
       <c r="X128" s="2" t="inlineStr"/>
+      <c r="Y128" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z128" s="2" t="inlineStr">
+        <is>
+          <t>타나, 카베르네 소비뇽, 카베르네 프랑, 메를로, 쁘띠 베르도·마쎌란</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -12506,6 +13778,16 @@
         <v>4</v>
       </c>
       <c r="X129" s="2" t="inlineStr"/>
+      <c r="Y129" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z129" s="2" t="inlineStr">
+        <is>
+          <t>카베르네 소비뇽, 메를로, 말벡</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -12602,6 +13884,16 @@
         <v>1</v>
       </c>
       <c r="X130" s="2" t="inlineStr"/>
+      <c r="Y130" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z130" s="2" t="inlineStr">
+        <is>
+          <t>샤도네이, 비오니에</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -12698,6 +13990,16 @@
         <v>4</v>
       </c>
       <c r="X131" s="2" t="inlineStr"/>
+      <c r="Y131" s="2" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="Z131" s="2" t="inlineStr">
+        <is>
+          <t>카베르네 프랑, 카르메네르</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13724,7 +15026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -13768,12 +15070,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>- 보틀 이미지: public/images/wines/&lt;id&gt;.png. 실제 제품 사진으로 교체할 때 같은 파일명으로 덮어쓰면 됨.</t>
+          <t>- 프로필 상태: estimated(규칙으로 산출한 추정치, 앱에 '검수 전' 표시) / verified(시음 검수 완료). 검수한 와인만 verified로 바꿀 것.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>- 품종 태그: 비워두면 품종 컬럼에서 자동 생성됨. 필터에 쓰이므로 표기를 통일할 것 (예: 피노 누아, 토우리가 나시오날).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>- 보틀 이미지: public/images/wines/&lt;id&gt;.png. 실제 제품 사진으로 교체할 때 같은 파일명으로 덮어쓰면 됨.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>- 수정 후: python scripts/build_data.py 실행 -&gt; src/data/*.json 갱신 -&gt; git push 하면 자동 배포.</t>
         </is>
